--- a/survey_templates/045_flashcard_creation_survey--survey_templates.xlsx
+++ b/survey_templates/045_flashcard_creation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -713,7 +713,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Platform Other</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Content Other</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Frequency Use Other</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -957,8 +957,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': 'Yearly'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_'images'}</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': 'Images'}</t>
+          <t>Images</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_'videos'}</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': 'Videos'}</t>
+          <t>Videos</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_'audio'}</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': 'Audio'}</t>
+          <t>Audio</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'text':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'text': 'Text'}</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'text':_'mix'}</t>
+          <t>mix</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'text': 'Mix'}</t>
+          <t>Mix</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'text':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'text': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'text':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'text': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'text':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'text': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'text':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'text': 'Yearly'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'text':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'text': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'text':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'text': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'text':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'text': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'text':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'text': 'Yearly'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'text':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'text': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'text':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'text': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'text':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'text': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'text':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'text': 'Yearly'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'text':_'anki'}</t>
+          <t>anki</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'text': 'Anki'}</t>
+          <t>Anki</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'text':_'quizlet'}</t>
+          <t>quizlet</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'text': 'Quizlet'}</t>
+          <t>Quizlet</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'text':_'ankidroid'}</t>
+          <t>ankidroid</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'text': 'AnkiDroid'}</t>
+          <t>AnkiDroid</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'text':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'text': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'text':_'vocab'}</t>
+          <t>vocab</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'text': 'Vocab'}</t>
+          <t>Vocab</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'text':_'grammar'}</t>
+          <t>grammar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'text': 'Grammar'}</t>
+          <t>Grammar</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'text':_'idioms'}</t>
+          <t>idioms</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'text': 'Idioms'}</t>
+          <t>Idioms</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'text':_'formula'}</t>
+          <t>formula</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'text': 'Formula'}</t>
+          <t>Formula</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'text':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'text': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
